--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="130">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:23:27+00:00</t>
+    <t>2026-09-29T07:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,6 +333,15 @@
     <t>as-bal-mss-cab.adresse</t>
   </si>
   <si>
+    <t>as-bal-mss-cab.identifiantPP</t>
+  </si>
+  <si>
+    <t>Identifiant PP</t>
+  </si>
+  <si>
+    <t>Identifiant national du professionnel de santé (RPPS)</t>
+  </si>
+  <si>
     <t>as-bal-mss-cab.description</t>
   </si>
   <si>
@@ -393,10 +402,7 @@
     <t>as-bal-mss-per.identifiantPP</t>
   </si>
   <si>
-    <t>Identifiant PP</t>
-  </si>
-  <si>
-    <t>Identifiant national du professionnel de santé (RPPS)</t>
+    <t>as-bal-mss-per.description</t>
   </si>
   <si>
     <t>as-bal-mss-per.listeRouge</t>
@@ -877,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45">
@@ -885,7 +891,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46">
@@ -901,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48">
@@ -909,7 +915,7 @@
         <v>10</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49">
@@ -963,7 +969,7 @@
         <v>23</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56">
@@ -999,7 +1005,7 @@
         <v>31</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61">
@@ -1039,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66">
@@ -1047,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
@@ -1063,7 +1069,7 @@
         <v>8</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69">
@@ -1071,7 +1077,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70">
@@ -1125,7 +1131,7 @@
         <v>23</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77">
@@ -1161,7 +1167,7 @@
         <v>31</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82">
@@ -1195,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.90234375" customWidth="true" bestFit="true"/>
@@ -2291,7 +2297,7 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
@@ -2309,10 +2315,10 @@
         <v>81</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -2366,7 +2372,7 @@
         <v>105</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>80</v>
@@ -2383,10 +2389,10 @@
         <v>99</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -2409,13 +2415,13 @@
         <v>74</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -2466,7 +2472,7 @@
         <v>74</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>75</v>
@@ -2483,13 +2489,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -2500,7 +2506,7 @@
         <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>74</v>
@@ -2512,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2569,13 +2575,13 @@
         <v>74</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>74</v>
@@ -2586,13 +2592,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -2600,10 +2606,10 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>74</v>
@@ -2615,13 +2621,13 @@
         <v>74</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2672,13 +2678,13 @@
         <v>74</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>74</v>
@@ -2689,13 +2695,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -2721,10 +2727,10 @@
         <v>81</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2775,7 +2781,7 @@
         <v>74</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>80</v>
@@ -2792,13 +2798,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -2806,7 +2812,7 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -2824,10 +2830,10 @@
         <v>81</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -2878,10 +2884,10 @@
         <v>74</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -2895,13 +2901,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -2927,10 +2933,10 @@
         <v>81</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2981,7 +2987,7 @@
         <v>74</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>75</v>
@@ -2998,13 +3004,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3030,10 +3036,10 @@
         <v>81</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3084,7 +3090,7 @@
         <v>74</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>75</v>
@@ -3101,13 +3107,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -3130,13 +3136,13 @@
         <v>74</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -3187,7 +3193,7 @@
         <v>74</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>75</v>
@@ -3204,13 +3210,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -3221,7 +3227,7 @@
         <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>
@@ -3233,13 +3239,13 @@
         <v>74</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3290,13 +3296,13 @@
         <v>74</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>74</v>
@@ -3307,13 +3313,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3321,10 +3327,10 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3336,13 +3342,13 @@
         <v>74</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -3393,13 +3399,13 @@
         <v>74</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>74</v>
@@ -3410,13 +3416,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3442,10 +3448,10 @@
         <v>81</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3496,7 +3502,7 @@
         <v>74</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>80</v>
@@ -3513,7 +3519,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>127</v>
@@ -3527,7 +3533,7 @@
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -3542,13 +3548,13 @@
         <v>74</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -3602,15 +3608,221 @@
         <v>127</v>
       </c>
       <c r="AH23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK23" t="s" s="2">
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T07:26:07+00:00</t>
+    <t>2026-09-30T08:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapshot</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:41:32+00:00</t>
+    <t>2026-10-09T06:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:18:26+00:00</t>
+    <t>2026-10-09T06:22:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
